--- a/projects/paper-wista-r-efficiency-v3/_book/Tabellen-Effiziente-Analyse-Forschungsdaten-R.xlsx
+++ b/projects/paper-wista-r-efficiency-v3/_book/Tabellen-Effiziente-Analyse-Forschungsdaten-R.xlsx
@@ -6,14 +6,14 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="tbl-stba-rserver" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tbl-fdz-server" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="tbl-dplyr-syntax" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tbl-baseline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="tbl-benchmark-small" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="tbl-benchmark-regr-small" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="tbl-benchmark" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="tbl-benchmark-regr" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tabelle 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tabelle 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tabelle 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tabelle 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tabelle 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tabelle 6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Tabelle 7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Tabelle 8" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -21,6 +21,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
+    <t xml:space="preserve">Ausbau des R-Server des Statistischen Bundesamtes (Januar 2025)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Komponente</t>
   </si>
   <si>
@@ -73,9 +76,6 @@
   </si>
   <si>
     <t xml:space="preserve">je 2x A6000 (je 48 GB VRAM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ausbau des R-Server des Statistischen Bundesamtes (Januar 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">OnSite-Server des FDZ Bund: Spezifikationen (November 2025)</t>
@@ -768,90 +768,75 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +861,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>20</v>
@@ -900,7 +885,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -908,7 +893,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
@@ -1078,7 +1063,7 @@
         <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>52</v>
@@ -1190,7 +1175,7 @@
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>53</v>
@@ -1434,7 +1419,7 @@
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>53</v>
@@ -1518,7 +1503,7 @@
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>53</v>
@@ -1762,7 +1747,7 @@
         <v>69</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>53</v>
